--- a/VJC1225 text.xlsx
+++ b/VJC1225 text.xlsx
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="VHF" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -68,7 +68,7 @@
   <numFmts count="1">
     <numFmt numFmtId="165" formatCode="[h]:mm:ss;@"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -80,6 +80,13 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -102,11 +109,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="21" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -444,11 +452,15 @@
       <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TSN Tower, VJC1225 on the ILSw approach RWY 25R</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tan Son Nhat Tower vietjet one two two five on the ils wishky approach runway two five right</t>
+        </is>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.4">
